--- a/artfynd/A 24759-2020 artfynd.xlsx
+++ b/artfynd/A 24759-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120902612</v>
+        <v>120902615</v>
       </c>
       <c r="B2" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -728,21 +728,16 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Hofors, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563899</v>
+        <v>563830</v>
       </c>
       <c r="R2" t="n">
-        <v>6715421</v>
+        <v>6715423</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -784,12 +779,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 hanar hördes spela mot kallhygge och sjön , Calluna AB, SKH013b</t>
+          <t>Hördes spela, Calluna AB, SKH013b</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -816,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120902615</v>
+        <v>120902612</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -851,7 +846,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -869,16 +864,21 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Hofors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563830</v>
+        <v>563899</v>
       </c>
       <c r="R3" t="n">
-        <v>6715423</v>
+        <v>6715421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hördes spela, Calluna AB, SKH013b</t>
+          <t>2 hanar hördes spela mot kallhygge och sjön , Calluna AB, SKH013b</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24759-2020 artfynd.xlsx
+++ b/artfynd/A 24759-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120902615</v>
+        <v>120902612</v>
       </c>
       <c r="B2" t="n">
         <v>56566</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -728,16 +728,21 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Hofors, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563830</v>
+        <v>563899</v>
       </c>
       <c r="R2" t="n">
-        <v>6715423</v>
+        <v>6715421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +774,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,12 +784,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>05:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hördes spela, Calluna AB, SKH013b</t>
+          <t>2 hanar hördes spela mot kallhygge och sjön , Calluna AB, SKH013b</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,7 +816,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120902612</v>
+        <v>120902615</v>
       </c>
       <c r="B3" t="n">
         <v>56566</v>
@@ -846,7 +851,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -864,21 +869,16 @@
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>NV om Hofors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563899</v>
+        <v>563830</v>
       </c>
       <c r="R3" t="n">
-        <v>6715421</v>
+        <v>6715423</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:41</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 hanar hördes spela mot kallhygge och sjön , Calluna AB, SKH013b</t>
+          <t>Hördes spela, Calluna AB, SKH013b</t>
         </is>
       </c>
       <c r="AD3" t="b">
